--- a/chap07-express/uploads/엑셀연습1.xlsx
+++ b/chap07-express/uploads/엑셀연습1.xlsx
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t xml:space="preserve">user_id</t>
   </si>
@@ -65,6 +65,12 @@
   </si>
   <si>
     <t xml:space="preserve">김길동</t>
+  </si>
+  <si>
+    <t xml:space="preserve">admin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">관리자</t>
   </si>
 </sst>
 </file>
@@ -274,7 +280,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultColWidth="11.640625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -300,13 +306,24 @@
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="0" t="n">
+      <c r="C3" s="1" t="n">
+        <v>2345</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="0" t="n">
         <v>2345</v>
       </c>
     </row>
